--- a/tasks/finalpool/canvas-enrollment-overview/groundtruth_workspace/Canvas_Enrollment_Report.xlsx
+++ b/tasks/finalpool/canvas-enrollment-overview/groundtruth_workspace/Canvas_Enrollment_Report.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -50,9 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,38 +414,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Course_Code</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Course_Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Students</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Teachers</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>TAs</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Enrolled</t>
         </is>
       </c>
     </row>
@@ -470,12 +456,6 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>385</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -494,12 +474,6 @@
       <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>369</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -518,12 +492,6 @@
       <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1770</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -542,12 +510,6 @@
       <c r="D5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2241</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -566,12 +528,6 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1615</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -590,12 +546,6 @@
       <c r="D7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2296</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -614,12 +564,6 @@
       <c r="D8" t="n">
         <v>2</v>
       </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1940</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -638,12 +582,6 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2501</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -662,12 +600,6 @@
       <c r="D10" t="n">
         <v>2</v>
       </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1307</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -686,12 +618,6 @@
       <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1942</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -710,12 +636,6 @@
       <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1232</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -734,12 +654,6 @@
       <c r="D13" t="n">
         <v>2</v>
       </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1807</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -758,12 +672,6 @@
       <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1054</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -782,12 +690,6 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>696</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -806,12 +708,6 @@
       <c r="D16" t="n">
         <v>2</v>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1191</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -830,12 +726,6 @@
       <c r="D17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1617</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -854,12 +744,6 @@
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2285</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -878,12 +762,6 @@
       <c r="D19" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1502</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -902,12 +780,6 @@
       <c r="D20" t="n">
         <v>4</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2369</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -926,12 +798,6 @@
       <c r="D21" t="n">
         <v>2</v>
       </c>
-      <c r="E21" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>956</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -950,12 +816,6 @@
       <c r="D22" t="n">
         <v>1</v>
       </c>
-      <c r="E22" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>836</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -973,12 +833,6 @@
       </c>
       <c r="D23" t="n">
         <v>3</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>752</v>
       </c>
     </row>
   </sheetData>
@@ -996,12 +850,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
